--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-08-24 至 2026-09-06</t>
+    <t>2026-08-31 至 2026-09-13</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C1" s="2">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="D1" s="2">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="E1" s="2">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="F1" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="G1" s="2">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="H1" s="2">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="I1" s="2">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="J1" s="2">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="K1" s="2">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="L1" s="2">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="M1" s="2">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="N1" s="2">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="O1" s="2">
-        <v>46271</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>11397</v>
+        <v>9333</v>
       </c>
       <c r="C2" s="4">
-        <v>16641</v>
+        <v>9414</v>
       </c>
       <c r="D2" s="4">
-        <v>11635</v>
+        <v>10534</v>
       </c>
       <c r="E2" s="4">
-        <v>11495</v>
+        <v>6476</v>
       </c>
       <c r="F2" s="4">
-        <v>9037</v>
+        <v>9101</v>
       </c>
       <c r="G2" s="4">
-        <v>10856</v>
+        <v>8226</v>
       </c>
       <c r="H2" s="4">
-        <v>9427</v>
+        <v>11803</v>
       </c>
       <c r="I2" s="4">
-        <v>9333</v>
+        <v>8873</v>
       </c>
       <c r="J2" s="4">
-        <v>9414</v>
+        <v>9498</v>
       </c>
       <c r="K2" s="4">
-        <v>10534</v>
+        <v>8838</v>
       </c>
       <c r="L2" s="4">
-        <v>6476</v>
+        <v>12520</v>
       </c>
       <c r="M2" s="4">
-        <v>9101</v>
+        <v>6519</v>
       </c>
       <c r="N2" s="4">
-        <v>8226</v>
+        <v>8625</v>
       </c>
       <c r="O2" s="4">
-        <v>11395</v>
+        <v>7790</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1354</v>
+        <v>1391</v>
       </c>
       <c r="C3" s="4">
-        <v>1375</v>
+        <v>1409</v>
       </c>
       <c r="D3" s="4">
+        <v>1584</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1003</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1505</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1284</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1860</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1315</v>
+      </c>
+      <c r="J3" s="4">
         <v>1383</v>
       </c>
-      <c r="E3" s="4">
-        <v>1532</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1473</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1692</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1534</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1391</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1409</v>
-      </c>
       <c r="K3" s="4">
-        <v>1584</v>
+        <v>1065</v>
       </c>
       <c r="L3" s="4">
-        <v>1003</v>
+        <v>1836</v>
       </c>
       <c r="M3" s="4">
-        <v>1505</v>
+        <v>1016</v>
       </c>
       <c r="N3" s="4">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="O3" s="4">
-        <v>1860</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.11880319382293586</v>
+        <v>0.14904103717989928</v>
       </c>
       <c r="C4" s="5">
-        <v>0.08262724595877652</v>
+        <v>0.14967070320798812</v>
       </c>
       <c r="D4" s="5">
-        <v>0.11886549204984959</v>
+        <v>0.1503702297322954</v>
       </c>
       <c r="E4" s="5">
-        <v>0.1332753371030883</v>
+        <v>0.15487955528103767</v>
       </c>
       <c r="F4" s="5">
-        <v>0.16299656965807238</v>
+        <v>0.16536644324799474</v>
       </c>
       <c r="G4" s="5">
-        <v>0.15585851142225499</v>
+        <v>0.1560904449307075</v>
       </c>
       <c r="H4" s="5">
-        <v>0.16272409037869948</v>
+        <v>0.15758705413877827</v>
       </c>
       <c r="I4" s="5">
-        <v>0.14904103717989928</v>
+        <v>0.14820241181111235</v>
       </c>
       <c r="J4" s="5">
-        <v>0.14967070320798812</v>
+        <v>0.1456096020214782</v>
       </c>
       <c r="K4" s="5">
-        <v>0.1503702297322954</v>
+        <v>0.12050237610319077</v>
       </c>
       <c r="L4" s="5">
-        <v>0.15487955528103767</v>
+        <v>0.14664536741214057</v>
       </c>
       <c r="M4" s="5">
-        <v>0.16536644324799474</v>
+        <v>0.15585212455898143</v>
       </c>
       <c r="N4" s="5">
-        <v>0.1560904449307075</v>
+        <v>0.1500289855072464</v>
       </c>
       <c r="O4" s="5">
-        <v>0.16322948661693726</v>
+        <v>0.1410783055198973</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.4867060561299852</v>
+        <v>1.3975557153127247</v>
       </c>
       <c r="C5" s="6">
-        <v>1.456</v>
+        <v>1.4300922640170333</v>
       </c>
       <c r="D5" s="6">
-        <v>1.5061460592913956</v>
+        <v>1.4659090909090908</v>
       </c>
       <c r="E5" s="6">
-        <v>1.4471279373368147</v>
+        <v>1.5692921236291126</v>
       </c>
       <c r="F5" s="6">
-        <v>1.442634080108622</v>
+        <v>1.521594684385382</v>
       </c>
       <c r="G5" s="6">
-        <v>1.4497635933806146</v>
+        <v>1.4742990654205608</v>
       </c>
       <c r="H5" s="6">
-        <v>1.485006518904824</v>
+        <v>1.4919354838709677</v>
       </c>
       <c r="I5" s="6">
-        <v>1.3975557153127247</v>
+        <v>1.4988593155893537</v>
       </c>
       <c r="J5" s="6">
-        <v>1.4300922640170333</v>
+        <v>1.3781634128705713</v>
       </c>
       <c r="K5" s="6">
-        <v>1.4659090909090908</v>
+        <v>1.4338028169014085</v>
       </c>
       <c r="L5" s="6">
-        <v>1.5692921236291126</v>
+        <v>1.3899782135076253</v>
       </c>
       <c r="M5" s="6">
-        <v>1.521594684385382</v>
+        <v>1.5049212598425197</v>
       </c>
       <c r="N5" s="6">
-        <v>1.4742990654205608</v>
+        <v>1.5247295208655331</v>
       </c>
       <c r="O5" s="6">
-        <v>1.4919354838709677</v>
+        <v>1.5559599636032757</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D6" s="4">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="E6" s="4">
-        <v>338</v>
+        <v>240</v>
       </c>
       <c r="F6" s="4">
+        <v>372</v>
+      </c>
+      <c r="G6" s="4">
         <v>313</v>
       </c>
-      <c r="G6" s="4">
-        <v>375</v>
-      </c>
       <c r="H6" s="4">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="I6" s="4">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="J6" s="4">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="K6" s="4">
-        <v>357</v>
+        <v>233</v>
       </c>
       <c r="L6" s="4">
-        <v>240</v>
+        <v>406</v>
       </c>
       <c r="M6" s="4">
-        <v>372</v>
+        <v>243</v>
       </c>
       <c r="N6" s="4">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="O6" s="4">
-        <v>410</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.23559822747415066</v>
+        <v>0.20848310567936737</v>
       </c>
       <c r="C7" s="5">
-        <v>0.22472727272727272</v>
+        <v>0.21220723917672107</v>
       </c>
       <c r="D7" s="5">
-        <v>0.23571945046999276</v>
+        <v>0.22537878787878787</v>
       </c>
       <c r="E7" s="5">
-        <v>0.2206266318537859</v>
+        <v>0.23928215353938184</v>
       </c>
       <c r="F7" s="5">
-        <v>0.21249151391717583</v>
+        <v>0.24717607973421926</v>
       </c>
       <c r="G7" s="5">
-        <v>0.22163120567375885</v>
+        <v>0.24376947040498442</v>
       </c>
       <c r="H7" s="5">
-        <v>0.23598435462842243</v>
+        <v>0.22043010752688172</v>
       </c>
       <c r="I7" s="5">
-        <v>0.20848310567936737</v>
+        <v>0.23041825095057034</v>
       </c>
       <c r="J7" s="5">
-        <v>0.21220723917672107</v>
+        <v>0.20535068691250905</v>
       </c>
       <c r="K7" s="5">
-        <v>0.22537878787878787</v>
+        <v>0.2187793427230047</v>
       </c>
       <c r="L7" s="5">
-        <v>0.23928215353938184</v>
+        <v>0.22113289760348584</v>
       </c>
       <c r="M7" s="5">
-        <v>0.24717607973421926</v>
+        <v>0.23917322834645668</v>
       </c>
       <c r="N7" s="5">
-        <v>0.24376947040498442</v>
+        <v>0.2534775888717156</v>
       </c>
       <c r="O7" s="5">
-        <v>0.22043010752688172</v>
+        <v>0.26660600545950863</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>866</v>
+        <v>595</v>
       </c>
       <c r="C8" s="4">
-        <v>814</v>
+        <v>613</v>
       </c>
       <c r="D8" s="4">
-        <v>862</v>
+        <v>671</v>
       </c>
       <c r="E8" s="4">
-        <v>788</v>
+        <v>478</v>
       </c>
       <c r="F8" s="4">
-        <v>712</v>
+        <v>738</v>
       </c>
       <c r="G8" s="4">
-        <v>826</v>
+        <v>663</v>
       </c>
       <c r="H8" s="4">
-        <v>766</v>
+        <v>920</v>
       </c>
       <c r="I8" s="4">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="J8" s="4">
-        <v>613</v>
+        <v>448</v>
       </c>
       <c r="K8" s="4">
-        <v>671</v>
+        <v>436</v>
       </c>
       <c r="L8" s="4">
-        <v>478</v>
+        <v>733</v>
       </c>
       <c r="M8" s="4">
-        <v>738</v>
+        <v>518</v>
       </c>
       <c r="N8" s="4">
-        <v>663</v>
+        <v>558</v>
       </c>
       <c r="O8" s="4">
-        <v>895</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="D9" s="4">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="E9" s="4">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="F9" s="4">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="G9" s="4">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="H9" s="4">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="I9" s="4">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="J9" s="4">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="K9" s="4">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="L9" s="4">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="M9" s="4">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="N9" s="4">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="O9" s="4">
-        <v>163</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.21709006928406466</v>
+        <v>0.1899159663865546</v>
       </c>
       <c r="C10" s="5">
-        <v>0.2199017199017199</v>
+        <v>0.17944535073409462</v>
       </c>
       <c r="D10" s="5">
-        <v>0.20765661252900233</v>
+        <v>0.17436661698956782</v>
       </c>
       <c r="E10" s="5">
-        <v>0.20558375634517767</v>
+        <v>0.21338912133891214</v>
       </c>
       <c r="F10" s="5">
-        <v>0.17696629213483145</v>
+        <v>0.19241192411924118</v>
       </c>
       <c r="G10" s="5">
-        <v>0.19975786924939468</v>
+        <v>0.16289592760180996</v>
       </c>
       <c r="H10" s="5">
-        <v>0.17493472584856398</v>
+        <v>0.18478260869565216</v>
       </c>
       <c r="I10" s="5">
-        <v>0.1899159663865546</v>
+        <v>0.12084063047285463</v>
       </c>
       <c r="J10" s="5">
-        <v>0.17944535073409462</v>
+        <v>0.11160714285714286</v>
       </c>
       <c r="K10" s="5">
-        <v>0.17436661698956782</v>
+        <v>0.10779816513761468</v>
       </c>
       <c r="L10" s="5">
-        <v>0.21338912133891214</v>
+        <v>0.1009549795361528</v>
       </c>
       <c r="M10" s="5">
-        <v>0.19241192411924118</v>
+        <v>0.055984555984555984</v>
       </c>
       <c r="N10" s="5">
-        <v>0.16289592760180996</v>
+        <v>0.1057347670250896</v>
       </c>
       <c r="O10" s="5">
-        <v>0.18212290502793296</v>
+        <v>0.21065989847715735</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,135 +1028,141 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="4">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4">
         <v>12</v>
       </c>
-      <c r="D11" s="4">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4">
-        <v>25</v>
-      </c>
       <c r="F11" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G11" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H11" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="4">
         <v>11</v>
       </c>
       <c r="L11" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M11" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N11" s="4">
-        <v>8</v>
-      </c>
-      <c r="O11" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="O11" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="4">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="E12" s="4">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>9</v>
+      </c>
+      <c r="G12" s="4">
         <v>7</v>
       </c>
-      <c r="E12" s="4">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="H12" s="4">
+        <v>7</v>
+      </c>
+      <c r="I12" s="4">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4">
+        <v>3</v>
+      </c>
+      <c r="K12" s="4">
         <v>2</v>
       </c>
-      <c r="G12" s="4">
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4">
         <v>2</v>
       </c>
-      <c r="H12" s="4">
+      <c r="N12" s="4">
         <v>2</v>
       </c>
-      <c r="I12" s="4">
-        <v>3</v>
-      </c>
-      <c r="J12" s="4">
-        <v>5</v>
-      </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
-        <v>9</v>
-      </c>
-      <c r="M12" s="4">
-        <v>9</v>
-      </c>
-      <c r="N12" s="4">
-        <v>7</v>
-      </c>
-      <c r="O12" s="4"/>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M13" s="5">
         <v>0.5</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.56</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0.9</v>
-      </c>
       <c r="N13" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="O13" s="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -1166,13 +1172,13 @@
         <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1184,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
@@ -1201,7 +1207,9 @@
       <c r="N14" s="4">
         <v>0</v>
       </c>
-      <c r="O14" s="4"/>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -1217,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1229,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4">
         <v>0</v>
@@ -1246,25 +1254,27 @@
       <c r="N15" s="4">
         <v>0</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5">
-        <v>0.75</v>
-      </c>
+      <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -1314,7 +1324,9 @@
       <c r="N17" s="4">
         <v>0</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -1359,7 +1371,9 @@
       <c r="N18" s="4">
         <v>0</v>
       </c>
-      <c r="O18" s="4"/>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -1096,25 +1096,25 @@
         <v>7</v>
       </c>
       <c r="I12" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4">
         <v>3</v>
       </c>
       <c r="K12" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
       </c>
       <c r="M12" s="4">
+        <v>3</v>
+      </c>
+      <c r="N12" s="4">
+        <v>3</v>
+      </c>
+      <c r="O12" s="4">
         <v>2</v>
-      </c>
-      <c r="N12" s="4">
-        <v>2</v>
-      </c>
-      <c r="O12" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1143,25 +1143,25 @@
         <v>0.875</v>
       </c>
       <c r="I13" s="5">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J13" s="5">
         <v>0.6</v>
       </c>
       <c r="K13" s="5">
-        <v>0.18181818181818182</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="L13" s="5">
         <v>0.16666666666666666</v>
       </c>
       <c r="M13" s="5">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N13" s="5">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O13" s="5">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-08-31 至 2026-09-13</t>
+    <t>2026-09-07 至 2026-09-20</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="C1" s="2">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="D1" s="2">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="E1" s="2">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="F1" s="2">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="G1" s="2">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="H1" s="2">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="I1" s="2">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="J1" s="2">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="K1" s="2">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="L1" s="2">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="M1" s="2">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="N1" s="2">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="O1" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>9333</v>
+        <v>8873</v>
       </c>
       <c r="C2" s="4">
-        <v>9414</v>
+        <v>9498</v>
       </c>
       <c r="D2" s="4">
-        <v>10534</v>
+        <v>8838</v>
       </c>
       <c r="E2" s="4">
-        <v>6476</v>
+        <v>12520</v>
       </c>
       <c r="F2" s="4">
-        <v>9101</v>
+        <v>6519</v>
       </c>
       <c r="G2" s="4">
-        <v>8226</v>
+        <v>8625</v>
       </c>
       <c r="H2" s="4">
-        <v>11803</v>
+        <v>7790</v>
       </c>
       <c r="I2" s="4">
-        <v>8873</v>
+        <v>1034</v>
       </c>
       <c r="J2" s="4">
-        <v>9498</v>
+        <v>1409</v>
       </c>
       <c r="K2" s="4">
-        <v>8838</v>
+        <v>1482</v>
       </c>
       <c r="L2" s="4">
-        <v>12520</v>
+        <v>4096</v>
       </c>
       <c r="M2" s="4">
-        <v>6519</v>
+        <v>5121</v>
       </c>
       <c r="N2" s="4">
-        <v>8625</v>
+        <v>4684</v>
       </c>
       <c r="O2" s="4">
-        <v>7790</v>
+        <v>6622</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1391</v>
+        <v>1315</v>
       </c>
       <c r="C3" s="4">
-        <v>1409</v>
+        <v>1383</v>
       </c>
       <c r="D3" s="4">
-        <v>1584</v>
+        <v>1065</v>
       </c>
       <c r="E3" s="4">
-        <v>1003</v>
+        <v>1836</v>
       </c>
       <c r="F3" s="4">
-        <v>1505</v>
+        <v>1015</v>
       </c>
       <c r="G3" s="4">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="H3" s="4">
-        <v>1860</v>
+        <v>1099</v>
       </c>
       <c r="I3" s="4">
-        <v>1315</v>
+        <v>132</v>
       </c>
       <c r="J3" s="4">
-        <v>1383</v>
+        <v>200</v>
       </c>
       <c r="K3" s="4">
-        <v>1065</v>
+        <v>222</v>
       </c>
       <c r="L3" s="4">
-        <v>1836</v>
+        <v>540</v>
       </c>
       <c r="M3" s="4">
-        <v>1016</v>
+        <v>714</v>
       </c>
       <c r="N3" s="4">
-        <v>1294</v>
+        <v>662</v>
       </c>
       <c r="O3" s="4">
-        <v>1099</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.14904103717989928</v>
+        <v>0.14820241181111235</v>
       </c>
       <c r="C4" s="5">
-        <v>0.14967070320798812</v>
+        <v>0.1456096020214782</v>
       </c>
       <c r="D4" s="5">
-        <v>0.1503702297322954</v>
+        <v>0.12050237610319077</v>
       </c>
       <c r="E4" s="5">
-        <v>0.15487955528103767</v>
+        <v>0.14664536741214057</v>
       </c>
       <c r="F4" s="5">
-        <v>0.16536644324799474</v>
+        <v>0.15569872679858873</v>
       </c>
       <c r="G4" s="5">
-        <v>0.1560904449307075</v>
+        <v>0.1500289855072464</v>
       </c>
       <c r="H4" s="5">
-        <v>0.15758705413877827</v>
+        <v>0.1410783055198973</v>
       </c>
       <c r="I4" s="5">
-        <v>0.14820241181111235</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="J4" s="5">
-        <v>0.1456096020214782</v>
+        <v>0.14194464158977999</v>
       </c>
       <c r="K4" s="5">
-        <v>0.12050237610319077</v>
+        <v>0.14979757085020243</v>
       </c>
       <c r="L4" s="5">
-        <v>0.14664536741214057</v>
+        <v>0.1318359375</v>
       </c>
       <c r="M4" s="5">
-        <v>0.15585212455898143</v>
+        <v>0.13942589338019917</v>
       </c>
       <c r="N4" s="5">
-        <v>0.1500289855072464</v>
+        <v>0.14133219470538003</v>
       </c>
       <c r="O4" s="5">
-        <v>0.1410783055198973</v>
+        <v>0.16943521594684385</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.3975557153127247</v>
+        <v>1.4988593155893537</v>
       </c>
       <c r="C5" s="6">
-        <v>1.4300922640170333</v>
+        <v>1.3781634128705713</v>
       </c>
       <c r="D5" s="6">
-        <v>1.4659090909090908</v>
+        <v>1.4338028169014085</v>
       </c>
       <c r="E5" s="6">
-        <v>1.5692921236291126</v>
+        <v>1.3899782135076253</v>
       </c>
       <c r="F5" s="6">
-        <v>1.521594684385382</v>
+        <v>1.5064039408866996</v>
       </c>
       <c r="G5" s="6">
-        <v>1.4742990654205608</v>
+        <v>1.5247295208655331</v>
       </c>
       <c r="H5" s="6">
-        <v>1.4919354838709677</v>
+        <v>1.5559599636032757</v>
       </c>
       <c r="I5" s="6">
-        <v>1.4988593155893537</v>
+        <v>1.893939393939394</v>
       </c>
       <c r="J5" s="6">
-        <v>1.3781634128705713</v>
+        <v>1.565</v>
       </c>
       <c r="K5" s="6">
-        <v>1.4338028169014085</v>
+        <v>1.7162162162162162</v>
       </c>
       <c r="L5" s="6">
-        <v>1.3899782135076253</v>
+        <v>1.5611111111111111</v>
       </c>
       <c r="M5" s="6">
-        <v>1.5049212598425197</v>
+        <v>1.526610644257703</v>
       </c>
       <c r="N5" s="6">
-        <v>1.5247295208655331</v>
+        <v>1.5830815709969788</v>
       </c>
       <c r="O5" s="6">
-        <v>1.5559599636032757</v>
+        <v>1.5659536541889483</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C6" s="4">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="D6" s="4">
-        <v>357</v>
+        <v>233</v>
       </c>
       <c r="E6" s="4">
-        <v>240</v>
+        <v>406</v>
       </c>
       <c r="F6" s="4">
-        <v>372</v>
+        <v>243</v>
       </c>
       <c r="G6" s="4">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="H6" s="4">
-        <v>410</v>
+        <v>293</v>
       </c>
       <c r="I6" s="4">
-        <v>303</v>
+        <v>47</v>
       </c>
       <c r="J6" s="4">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="K6" s="4">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>406</v>
+        <v>122</v>
       </c>
       <c r="M6" s="4">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="N6" s="4">
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="O6" s="4">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.20848310567936737</v>
+        <v>0.23041825095057034</v>
       </c>
       <c r="C7" s="5">
-        <v>0.21220723917672107</v>
+        <v>0.20535068691250905</v>
       </c>
       <c r="D7" s="5">
-        <v>0.22537878787878787</v>
+        <v>0.2187793427230047</v>
       </c>
       <c r="E7" s="5">
-        <v>0.23928215353938184</v>
+        <v>0.22113289760348584</v>
       </c>
       <c r="F7" s="5">
-        <v>0.24717607973421926</v>
+        <v>0.23940886699507388</v>
       </c>
       <c r="G7" s="5">
-        <v>0.24376947040498442</v>
+        <v>0.2534775888717156</v>
       </c>
       <c r="H7" s="5">
-        <v>0.22043010752688172</v>
+        <v>0.26660600545950863</v>
       </c>
       <c r="I7" s="5">
-        <v>0.23041825095057034</v>
+        <v>0.3560606060606061</v>
       </c>
       <c r="J7" s="5">
-        <v>0.20535068691250905</v>
+        <v>0.25</v>
       </c>
       <c r="K7" s="5">
-        <v>0.2187793427230047</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L7" s="5">
-        <v>0.22113289760348584</v>
+        <v>0.22592592592592592</v>
       </c>
       <c r="M7" s="5">
-        <v>0.23917322834645668</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="N7" s="5">
-        <v>0.2534775888717156</v>
+        <v>0.27492447129909364</v>
       </c>
       <c r="O7" s="5">
-        <v>0.26660600545950863</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="C8" s="4">
-        <v>613</v>
+        <v>448</v>
       </c>
       <c r="D8" s="4">
-        <v>671</v>
+        <v>436</v>
       </c>
       <c r="E8" s="4">
-        <v>478</v>
+        <v>733</v>
       </c>
       <c r="F8" s="4">
-        <v>738</v>
+        <v>518</v>
       </c>
       <c r="G8" s="4">
-        <v>663</v>
+        <v>558</v>
       </c>
       <c r="H8" s="4">
-        <v>920</v>
+        <v>394</v>
       </c>
       <c r="I8" s="4">
-        <v>571</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4">
-        <v>448</v>
+        <v>58</v>
       </c>
       <c r="K8" s="4">
-        <v>436</v>
+        <v>58</v>
       </c>
       <c r="L8" s="4">
-        <v>733</v>
+        <v>177</v>
       </c>
       <c r="M8" s="4">
-        <v>518</v>
+        <v>251</v>
       </c>
       <c r="N8" s="4">
-        <v>558</v>
+        <v>266</v>
       </c>
       <c r="O8" s="4">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="D9" s="4">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="E9" s="4">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="F9" s="4">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="G9" s="4">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="H9" s="4">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="I9" s="4">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K9" s="4">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="L9" s="4">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="M9" s="4">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N9" s="4">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O9" s="4">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.1899159663865546</v>
+        <v>0.12084063047285463</v>
       </c>
       <c r="C10" s="5">
-        <v>0.17944535073409462</v>
+        <v>0.11160714285714286</v>
       </c>
       <c r="D10" s="5">
-        <v>0.17436661698956782</v>
+        <v>0.10779816513761468</v>
       </c>
       <c r="E10" s="5">
-        <v>0.21338912133891214</v>
+        <v>0.1009549795361528</v>
       </c>
       <c r="F10" s="5">
-        <v>0.19241192411924118</v>
+        <v>0.055984555984555984</v>
       </c>
       <c r="G10" s="5">
-        <v>0.16289592760180996</v>
+        <v>0.1057347670250896</v>
       </c>
       <c r="H10" s="5">
-        <v>0.18478260869565216</v>
+        <v>0.21065989847715735</v>
       </c>
       <c r="I10" s="5">
-        <v>0.12084063047285463</v>
+        <v>0.35</v>
       </c>
       <c r="J10" s="5">
-        <v>0.11160714285714286</v>
+        <v>0.13793103448275862</v>
       </c>
       <c r="K10" s="5">
-        <v>0.10779816513761468</v>
+        <v>0.22413793103448276</v>
       </c>
       <c r="L10" s="5">
-        <v>0.1009549795361528</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="M10" s="5">
-        <v>0.055984555984555984</v>
+        <v>0.2151394422310757</v>
       </c>
       <c r="N10" s="5">
-        <v>0.1057347670250896</v>
+        <v>0.20676691729323307</v>
       </c>
       <c r="O10" s="5">
-        <v>0.21065989847715735</v>
+        <v>0.14092140921409213</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,46 +1028,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4">
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G11" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H11" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4">
         <v>5</v>
       </c>
       <c r="K11" s="4">
+        <v>3</v>
+      </c>
+      <c r="L11" s="4">
+        <v>5</v>
+      </c>
+      <c r="M11" s="4">
+        <v>7</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4">
         <v>11</v>
-      </c>
-      <c r="L11" s="4">
-        <v>6</v>
-      </c>
-      <c r="M11" s="4">
-        <v>4</v>
-      </c>
-      <c r="N11" s="4">
-        <v>5</v>
-      </c>
-      <c r="O11" s="4">
-        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1075,34 +1075,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="C12" s="4">
-        <v>5</v>
-      </c>
       <c r="D12" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H12" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4">
         <v>3</v>
       </c>
       <c r="K12" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
@@ -1111,10 +1111,10 @@
         <v>3</v>
       </c>
       <c r="N12" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1122,46 +1122,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.42857142857142855</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="5">
-        <v>0.7142857142857143</v>
+        <v>0.6</v>
       </c>
       <c r="D13" s="5">
-        <v>0.7272727272727273</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="E13" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F13" s="5">
         <v>0.75</v>
       </c>
-      <c r="F13" s="5">
-        <v>0.9</v>
-      </c>
       <c r="G13" s="5">
-        <v>0.875</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="5">
-        <v>0.875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I13" s="5">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J13" s="5">
         <v>0.6</v>
       </c>
       <c r="K13" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
         <v>0.36363636363636365</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="N13" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="O13" s="5">
-        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1169,38 +1169,38 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
         <v>1</v>
       </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
       <c r="M14" s="4">
         <v>0</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4">
         <v>0</v>
@@ -1262,24 +1262,26 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>1</v>
-      </c>
+      <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-09-07 至 2026-09-20</t>
+    <t>2026-09-14 至 2026-09-27</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="C1" s="2">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="D1" s="2">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="E1" s="2">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="F1" s="2">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="G1" s="2">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="H1" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="I1" s="2">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="J1" s="2">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="K1" s="2">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="L1" s="2">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="M1" s="2">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N1" s="2">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="O1" s="2">
-        <v>46285</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>8873</v>
+        <v>1034</v>
       </c>
       <c r="C2" s="4">
-        <v>9498</v>
+        <v>1409</v>
       </c>
       <c r="D2" s="4">
-        <v>8838</v>
+        <v>1482</v>
       </c>
       <c r="E2" s="4">
-        <v>12520</v>
+        <v>4096</v>
       </c>
       <c r="F2" s="4">
-        <v>6519</v>
+        <v>5121</v>
       </c>
       <c r="G2" s="4">
-        <v>8625</v>
+        <v>4684</v>
       </c>
       <c r="H2" s="4">
-        <v>7790</v>
+        <v>7478</v>
       </c>
       <c r="I2" s="4">
-        <v>1034</v>
+        <v>9361</v>
       </c>
       <c r="J2" s="4">
-        <v>1409</v>
+        <v>7088</v>
       </c>
       <c r="K2" s="4">
-        <v>1482</v>
+        <v>6680</v>
       </c>
       <c r="L2" s="4">
-        <v>4096</v>
+        <v>6504</v>
       </c>
       <c r="M2" s="4">
-        <v>5121</v>
+        <v>11966</v>
       </c>
       <c r="N2" s="4">
-        <v>4684</v>
+        <v>10874</v>
       </c>
       <c r="O2" s="4">
-        <v>6622</v>
+        <v>12647</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1315</v>
+        <v>132</v>
       </c>
       <c r="C3" s="4">
-        <v>1383</v>
+        <v>200</v>
       </c>
       <c r="D3" s="4">
-        <v>1065</v>
+        <v>222</v>
       </c>
       <c r="E3" s="4">
-        <v>1836</v>
+        <v>540</v>
       </c>
       <c r="F3" s="4">
-        <v>1015</v>
+        <v>714</v>
       </c>
       <c r="G3" s="4">
-        <v>1294</v>
+        <v>662</v>
       </c>
       <c r="H3" s="4">
-        <v>1099</v>
+        <v>1122</v>
       </c>
       <c r="I3" s="4">
-        <v>132</v>
+        <v>1331</v>
       </c>
       <c r="J3" s="4">
-        <v>200</v>
+        <v>997</v>
       </c>
       <c r="K3" s="4">
-        <v>222</v>
+        <v>916</v>
       </c>
       <c r="L3" s="4">
-        <v>540</v>
+        <v>886</v>
       </c>
       <c r="M3" s="4">
-        <v>714</v>
+        <v>1519</v>
       </c>
       <c r="N3" s="4">
-        <v>662</v>
+        <v>1412</v>
       </c>
       <c r="O3" s="4">
-        <v>1122</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.14820241181111235</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="C4" s="5">
-        <v>0.1456096020214782</v>
+        <v>0.14194464158977999</v>
       </c>
       <c r="D4" s="5">
-        <v>0.12050237610319077</v>
+        <v>0.14979757085020243</v>
       </c>
       <c r="E4" s="5">
-        <v>0.14664536741214057</v>
+        <v>0.1318359375</v>
       </c>
       <c r="F4" s="5">
-        <v>0.15569872679858873</v>
+        <v>0.13942589338019917</v>
       </c>
       <c r="G4" s="5">
-        <v>0.1500289855072464</v>
+        <v>0.14133219470538003</v>
       </c>
       <c r="H4" s="5">
-        <v>0.1410783055198973</v>
+        <v>0.15004011767852368</v>
       </c>
       <c r="I4" s="5">
-        <v>0.1276595744680851</v>
+        <v>0.14218566392479437</v>
       </c>
       <c r="J4" s="5">
-        <v>0.14194464158977999</v>
+        <v>0.14066027088036118</v>
       </c>
       <c r="K4" s="5">
-        <v>0.14979757085020243</v>
+        <v>0.137125748502994</v>
       </c>
       <c r="L4" s="5">
-        <v>0.1318359375</v>
+        <v>0.13622386223862237</v>
       </c>
       <c r="M4" s="5">
-        <v>0.13942589338019917</v>
+        <v>0.12694300518134716</v>
       </c>
       <c r="N4" s="5">
-        <v>0.14133219470538003</v>
+        <v>0.12985102078352032</v>
       </c>
       <c r="O4" s="5">
-        <v>0.16943521594684385</v>
+        <v>0.13497272080335257</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.4988593155893537</v>
+        <v>1.893939393939394</v>
       </c>
       <c r="C5" s="6">
-        <v>1.3781634128705713</v>
+        <v>1.565</v>
       </c>
       <c r="D5" s="6">
-        <v>1.4338028169014085</v>
+        <v>1.7162162162162162</v>
       </c>
       <c r="E5" s="6">
-        <v>1.3899782135076253</v>
+        <v>1.5611111111111111</v>
       </c>
       <c r="F5" s="6">
-        <v>1.5064039408866996</v>
+        <v>1.526610644257703</v>
       </c>
       <c r="G5" s="6">
-        <v>1.5247295208655331</v>
+        <v>1.5830815709969788</v>
       </c>
       <c r="H5" s="6">
-        <v>1.5559599636032757</v>
+        <v>1.5659536541889483</v>
       </c>
       <c r="I5" s="6">
-        <v>1.893939393939394</v>
+        <v>1.5026296018031555</v>
       </c>
       <c r="J5" s="6">
-        <v>1.565</v>
+        <v>1.5757271815446339</v>
       </c>
       <c r="K5" s="6">
-        <v>1.7162162162162162</v>
+        <v>1.6200873362445414</v>
       </c>
       <c r="L5" s="6">
-        <v>1.5611111111111111</v>
+        <v>1.6376975169300225</v>
       </c>
       <c r="M5" s="6">
-        <v>1.526610644257703</v>
+        <v>1.4832126398946675</v>
       </c>
       <c r="N5" s="6">
-        <v>1.5830815709969788</v>
+        <v>1.5637393767705383</v>
       </c>
       <c r="O5" s="6">
-        <v>1.5659536541889483</v>
+        <v>1.5500878734622143</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>303</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="E6" s="4">
-        <v>406</v>
+        <v>122</v>
       </c>
       <c r="F6" s="4">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="G6" s="4">
-        <v>328</v>
+        <v>182</v>
       </c>
       <c r="H6" s="4">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I6" s="4">
-        <v>47</v>
+        <v>317</v>
       </c>
       <c r="J6" s="4">
-        <v>50</v>
+        <v>254</v>
       </c>
       <c r="K6" s="4">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="L6" s="4">
-        <v>122</v>
+        <v>227</v>
       </c>
       <c r="M6" s="4">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="N6" s="4">
-        <v>182</v>
+        <v>365</v>
       </c>
       <c r="O6" s="4">
-        <v>297</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.23041825095057034</v>
+        <v>0.3560606060606061</v>
       </c>
       <c r="C7" s="5">
-        <v>0.20535068691250905</v>
+        <v>0.25</v>
       </c>
       <c r="D7" s="5">
-        <v>0.2187793427230047</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E7" s="5">
-        <v>0.22113289760348584</v>
+        <v>0.22592592592592592</v>
       </c>
       <c r="F7" s="5">
-        <v>0.23940886699507388</v>
+        <v>0.24509803921568626</v>
       </c>
       <c r="G7" s="5">
-        <v>0.2534775888717156</v>
+        <v>0.27492447129909364</v>
       </c>
       <c r="H7" s="5">
-        <v>0.26660600545950863</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="I7" s="5">
-        <v>0.3560606060606061</v>
+        <v>0.23816679188580014</v>
       </c>
       <c r="J7" s="5">
-        <v>0.25</v>
+        <v>0.2547642928786359</v>
       </c>
       <c r="K7" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.24126637554585154</v>
       </c>
       <c r="L7" s="5">
-        <v>0.22592592592592592</v>
+        <v>0.2562076749435666</v>
       </c>
       <c r="M7" s="5">
-        <v>0.24509803921568626</v>
+        <v>0.23831468071099407</v>
       </c>
       <c r="N7" s="5">
-        <v>0.27492447129909364</v>
+        <v>0.2584985835694051</v>
       </c>
       <c r="O7" s="5">
-        <v>0.2647058823529412</v>
+        <v>0.24194493263034564</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>571</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4">
-        <v>448</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4">
-        <v>436</v>
+        <v>58</v>
       </c>
       <c r="E8" s="4">
-        <v>733</v>
+        <v>177</v>
       </c>
       <c r="F8" s="4">
-        <v>518</v>
+        <v>251</v>
       </c>
       <c r="G8" s="4">
-        <v>558</v>
+        <v>266</v>
       </c>
       <c r="H8" s="4">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="I8" s="4">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="J8" s="4">
-        <v>58</v>
+        <v>383</v>
       </c>
       <c r="K8" s="4">
-        <v>58</v>
+        <v>336</v>
       </c>
       <c r="L8" s="4">
-        <v>177</v>
+        <v>321</v>
       </c>
       <c r="M8" s="4">
-        <v>251</v>
+        <v>582</v>
       </c>
       <c r="N8" s="4">
-        <v>266</v>
+        <v>497</v>
       </c>
       <c r="O8" s="4">
-        <v>369</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C9" s="4">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E9" s="4">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G9" s="4">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H9" s="4">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="I9" s="4">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="J9" s="4">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="K9" s="4">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="L9" s="4">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="M9" s="4">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="N9" s="4">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O9" s="4">
-        <v>52</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.12084063047285463</v>
+        <v>0.35</v>
       </c>
       <c r="C10" s="5">
-        <v>0.11160714285714286</v>
+        <v>0.13793103448275862</v>
       </c>
       <c r="D10" s="5">
-        <v>0.10779816513761468</v>
+        <v>0.22413793103448276</v>
       </c>
       <c r="E10" s="5">
-        <v>0.1009549795361528</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="F10" s="5">
-        <v>0.055984555984555984</v>
+        <v>0.2151394422310757</v>
       </c>
       <c r="G10" s="5">
-        <v>0.1057347670250896</v>
+        <v>0.20676691729323307</v>
       </c>
       <c r="H10" s="5">
-        <v>0.21065989847715735</v>
+        <v>0.1383495145631068</v>
       </c>
       <c r="I10" s="5">
-        <v>0.35</v>
+        <v>0.14166666666666666</v>
       </c>
       <c r="J10" s="5">
-        <v>0.13793103448275862</v>
+        <v>0.1462140992167102</v>
       </c>
       <c r="K10" s="5">
-        <v>0.22413793103448276</v>
+        <v>0.1636904761904762</v>
       </c>
       <c r="L10" s="5">
-        <v>0.1864406779661017</v>
+        <v>0.17133956386292834</v>
       </c>
       <c r="M10" s="5">
-        <v>0.2151394422310757</v>
+        <v>0.12199312714776632</v>
       </c>
       <c r="N10" s="5">
-        <v>0.20676691729323307</v>
+        <v>0.13682092555331993</v>
       </c>
       <c r="O10" s="5">
-        <v>0.14092140921409213</v>
+        <v>0.13509060955518945</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,46 +1028,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4">
         <v>5</v>
       </c>
       <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
         <v>11</v>
       </c>
-      <c r="E11" s="4">
-        <v>6</v>
-      </c>
-      <c r="F11" s="4">
-        <v>4</v>
-      </c>
-      <c r="G11" s="4">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4">
-        <v>3</v>
-      </c>
       <c r="I11" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K11" s="4">
         <v>3</v>
       </c>
       <c r="L11" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N11" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O11" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1075,13 +1075,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4">
         <v>3</v>
       </c>
       <c r="D12" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
@@ -1090,31 +1090,31 @@
         <v>3</v>
       </c>
       <c r="G12" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
       </c>
       <c r="L12" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1122,46 +1122,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C13" s="5">
         <v>0.6</v>
       </c>
       <c r="D13" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
         <v>0.36363636363636365</v>
       </c>
-      <c r="E13" s="5">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="I13" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="5">
-        <v>0.6</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K13" s="5">
         <v>0.3333333333333333</v>
       </c>
       <c r="L13" s="5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M13" s="5">
-        <v>0.42857142857142855</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N13" s="5">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="O13" s="5">
-        <v>0.36363636363636365</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1169,7 +1169,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" s="4">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1187,19 +1187,19 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" s="4">
         <v>0</v>
@@ -1262,26 +1262,28 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
+      <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="5">
-        <v>0</v>
-      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
-      <c r="O16" s="5">
-        <v>0</v>
-      </c>
+      <c r="O16" s="5"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-09-14 至 2026-09-27</t>
+    <t>2026-09-28 至 2026-10-11</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="C1" s="2">
-        <v>46280</v>
+        <v>46294</v>
       </c>
       <c r="D1" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="E1" s="2">
-        <v>46282</v>
+        <v>46296</v>
       </c>
       <c r="F1" s="2">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="G1" s="2">
-        <v>46284</v>
+        <v>46298</v>
       </c>
       <c r="H1" s="2">
-        <v>46285</v>
+        <v>46299</v>
       </c>
       <c r="I1" s="2">
-        <v>46286</v>
+        <v>46300</v>
       </c>
       <c r="J1" s="2">
-        <v>46287</v>
+        <v>46301</v>
       </c>
       <c r="K1" s="2">
-        <v>46288</v>
+        <v>46302</v>
       </c>
       <c r="L1" s="2">
-        <v>46289</v>
+        <v>46303</v>
       </c>
       <c r="M1" s="2">
-        <v>46290</v>
+        <v>46304</v>
       </c>
       <c r="N1" s="2">
-        <v>46291</v>
+        <v>46305</v>
       </c>
       <c r="O1" s="2">
-        <v>46292</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1034</v>
+        <v>11134</v>
       </c>
       <c r="C2" s="4">
-        <v>1409</v>
+        <v>11757</v>
       </c>
       <c r="D2" s="4">
-        <v>1482</v>
+        <v>14039</v>
       </c>
       <c r="E2" s="4">
-        <v>4096</v>
+        <v>10810</v>
       </c>
       <c r="F2" s="4">
-        <v>5121</v>
+        <v>11219</v>
       </c>
       <c r="G2" s="4">
-        <v>4684</v>
+        <v>13855</v>
       </c>
       <c r="H2" s="4">
-        <v>7478</v>
+        <v>21135</v>
       </c>
       <c r="I2" s="4">
-        <v>9361</v>
+        <v>13995</v>
       </c>
       <c r="J2" s="4">
-        <v>7088</v>
+        <v>16639</v>
       </c>
       <c r="K2" s="4">
-        <v>6680</v>
+        <v>14719</v>
       </c>
       <c r="L2" s="4">
-        <v>6504</v>
+        <v>14243</v>
       </c>
       <c r="M2" s="4">
-        <v>11966</v>
+        <v>17675</v>
       </c>
       <c r="N2" s="4">
-        <v>10874</v>
+        <v>17329</v>
       </c>
       <c r="O2" s="4">
-        <v>12647</v>
+        <v>19390</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>132</v>
+        <v>1462</v>
       </c>
       <c r="C3" s="4">
-        <v>200</v>
+        <v>1530</v>
       </c>
       <c r="D3" s="4">
-        <v>222</v>
+        <v>1369</v>
       </c>
       <c r="E3" s="4">
-        <v>540</v>
+        <v>1070</v>
       </c>
       <c r="F3" s="4">
-        <v>714</v>
+        <v>1131</v>
       </c>
       <c r="G3" s="4">
-        <v>662</v>
+        <v>1466</v>
       </c>
       <c r="H3" s="4">
-        <v>1122</v>
+        <v>2073</v>
       </c>
       <c r="I3" s="4">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="J3" s="4">
-        <v>997</v>
+        <v>1710</v>
       </c>
       <c r="K3" s="4">
-        <v>916</v>
+        <v>1568</v>
       </c>
       <c r="L3" s="4">
-        <v>886</v>
+        <v>1325</v>
       </c>
       <c r="M3" s="4">
-        <v>1519</v>
+        <v>1634</v>
       </c>
       <c r="N3" s="4">
-        <v>1412</v>
+        <v>2052</v>
       </c>
       <c r="O3" s="4">
-        <v>1707</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.1276595744680851</v>
+        <v>0.1313095024250045</v>
       </c>
       <c r="C4" s="5">
-        <v>0.14194464158977999</v>
+        <v>0.13013523858127074</v>
       </c>
       <c r="D4" s="5">
-        <v>0.14979757085020243</v>
+        <v>0.09751406795355795</v>
       </c>
       <c r="E4" s="5">
-        <v>0.1318359375</v>
+        <v>0.09898242368177614</v>
       </c>
       <c r="F4" s="5">
-        <v>0.13942589338019917</v>
+        <v>0.10081112398609501</v>
       </c>
       <c r="G4" s="5">
-        <v>0.14133219470538003</v>
+        <v>0.10581017683146879</v>
       </c>
       <c r="H4" s="5">
-        <v>0.15004011767852368</v>
+        <v>0.09808374733853797</v>
       </c>
       <c r="I4" s="5">
-        <v>0.14218566392479437</v>
+        <v>0.09581993569131833</v>
       </c>
       <c r="J4" s="5">
-        <v>0.14066027088036118</v>
+        <v>0.10277059919466314</v>
       </c>
       <c r="K4" s="5">
-        <v>0.137125748502994</v>
+        <v>0.10652897615327128</v>
       </c>
       <c r="L4" s="5">
-        <v>0.13622386223862237</v>
+        <v>0.09302815418100119</v>
       </c>
       <c r="M4" s="5">
-        <v>0.12694300518134716</v>
+        <v>0.09244695898161245</v>
       </c>
       <c r="N4" s="5">
-        <v>0.12985102078352032</v>
+        <v>0.11841421893935022</v>
       </c>
       <c r="O4" s="5">
-        <v>0.13497272080335257</v>
+        <v>0.137648272305312</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.893939393939394</v>
+        <v>1.4452804377564978</v>
       </c>
       <c r="C5" s="6">
-        <v>1.565</v>
+        <v>1.5143790849673202</v>
       </c>
       <c r="D5" s="6">
-        <v>1.7162162162162162</v>
+        <v>1.5135135135135136</v>
       </c>
       <c r="E5" s="6">
-        <v>1.5611111111111111</v>
+        <v>1.3831775700934579</v>
       </c>
       <c r="F5" s="6">
-        <v>1.526610644257703</v>
+        <v>1.4367816091954022</v>
       </c>
       <c r="G5" s="6">
-        <v>1.5830815709969788</v>
+        <v>1.4311050477489768</v>
       </c>
       <c r="H5" s="6">
-        <v>1.5659536541889483</v>
+        <v>1.442836468885673</v>
       </c>
       <c r="I5" s="6">
-        <v>1.5026296018031555</v>
+        <v>1.4556301267710663</v>
       </c>
       <c r="J5" s="6">
-        <v>1.5757271815446339</v>
+        <v>1.4210526315789473</v>
       </c>
       <c r="K5" s="6">
-        <v>1.6200873362445414</v>
+        <v>1.4732142857142858</v>
       </c>
       <c r="L5" s="6">
-        <v>1.6376975169300225</v>
+        <v>1.5192452830188679</v>
       </c>
       <c r="M5" s="6">
-        <v>1.4832126398946675</v>
+        <v>1.5379436964504285</v>
       </c>
       <c r="N5" s="6">
-        <v>1.5637393767705383</v>
+        <v>1.5243664717348928</v>
       </c>
       <c r="O5" s="6">
-        <v>1.5500878734622143</v>
+        <v>1.5395279130760584</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>47</v>
+        <v>345</v>
       </c>
       <c r="C6" s="4">
-        <v>50</v>
+        <v>369</v>
       </c>
       <c r="D6" s="4">
-        <v>74</v>
+        <v>335</v>
       </c>
       <c r="E6" s="4">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="F6" s="4">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="G6" s="4">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="H6" s="4">
-        <v>297</v>
+        <v>453</v>
       </c>
       <c r="I6" s="4">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="J6" s="4">
-        <v>254</v>
+        <v>369</v>
       </c>
       <c r="K6" s="4">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="L6" s="4">
-        <v>227</v>
+        <v>304</v>
       </c>
       <c r="M6" s="4">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="N6" s="4">
-        <v>365</v>
+        <v>485</v>
       </c>
       <c r="O6" s="4">
-        <v>413</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.3560606060606061</v>
+        <v>0.2359781121751026</v>
       </c>
       <c r="C7" s="5">
-        <v>0.25</v>
+        <v>0.2411764705882353</v>
       </c>
       <c r="D7" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.24470416362308253</v>
       </c>
       <c r="E7" s="5">
-        <v>0.22592592592592592</v>
+        <v>0.20186915887850468</v>
       </c>
       <c r="F7" s="5">
-        <v>0.24509803921568626</v>
+        <v>0.21220159151193635</v>
       </c>
       <c r="G7" s="5">
-        <v>0.27492447129909364</v>
+        <v>0.20668485675306958</v>
       </c>
       <c r="H7" s="5">
-        <v>0.2647058823529412</v>
+        <v>0.21852387843704776</v>
       </c>
       <c r="I7" s="5">
-        <v>0.23816679188580014</v>
+        <v>0.2244593586875466</v>
       </c>
       <c r="J7" s="5">
-        <v>0.2547642928786359</v>
+        <v>0.21578947368421053</v>
       </c>
       <c r="K7" s="5">
-        <v>0.24126637554585154</v>
+        <v>0.22385204081632654</v>
       </c>
       <c r="L7" s="5">
-        <v>0.2562076749435666</v>
+        <v>0.22943396226415094</v>
       </c>
       <c r="M7" s="5">
-        <v>0.23831468071099407</v>
+        <v>0.23684210526315788</v>
       </c>
       <c r="N7" s="5">
-        <v>0.2584985835694051</v>
+        <v>0.23635477582846004</v>
       </c>
       <c r="O7" s="5">
-        <v>0.24194493263034564</v>
+        <v>0.24203821656050956</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="C8" s="4">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="D8" s="4">
-        <v>58</v>
+        <v>406</v>
       </c>
       <c r="E8" s="4">
-        <v>177</v>
+        <v>303</v>
       </c>
       <c r="F8" s="4">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="G8" s="4">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="H8" s="4">
-        <v>412</v>
+        <v>608</v>
       </c>
       <c r="I8" s="4">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="J8" s="4">
-        <v>383</v>
+        <v>507</v>
       </c>
       <c r="K8" s="4">
-        <v>336</v>
+        <v>455</v>
       </c>
       <c r="L8" s="4">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="M8" s="4">
-        <v>582</v>
+        <v>519</v>
       </c>
       <c r="N8" s="4">
-        <v>497</v>
+        <v>680</v>
       </c>
       <c r="O8" s="4">
-        <v>607</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D9" s="4">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="E9" s="4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F9" s="4">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G9" s="4">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H9" s="4">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I9" s="4">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="J9" s="4">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="K9" s="4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L9" s="4">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M9" s="4">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N9" s="4">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="O9" s="4">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.35</v>
+        <v>0.3283582089552239</v>
       </c>
       <c r="C10" s="5">
-        <v>0.13793103448275862</v>
+        <v>0.32270916334661354</v>
       </c>
       <c r="D10" s="5">
-        <v>0.22413793103448276</v>
+        <v>0.11576354679802955</v>
       </c>
       <c r="E10" s="5">
-        <v>0.1864406779661017</v>
+        <v>0.0891089108910891</v>
       </c>
       <c r="F10" s="5">
-        <v>0.2151394422310757</v>
+        <v>0.09539473684210527</v>
       </c>
       <c r="G10" s="5">
-        <v>0.20676691729323307</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="H10" s="5">
-        <v>0.1383495145631068</v>
+        <v>0.14473684210526316</v>
       </c>
       <c r="I10" s="5">
-        <v>0.14166666666666666</v>
+        <v>0.13111111111111112</v>
       </c>
       <c r="J10" s="5">
-        <v>0.1462140992167102</v>
+        <v>0.1873767258382643</v>
       </c>
       <c r="K10" s="5">
-        <v>0.1636904761904762</v>
+        <v>0.10989010989010989</v>
       </c>
       <c r="L10" s="5">
-        <v>0.17133956386292834</v>
+        <v>0.1760204081632653</v>
       </c>
       <c r="M10" s="5">
-        <v>0.12199312714776632</v>
+        <v>0.16377649325626203</v>
       </c>
       <c r="N10" s="5">
-        <v>0.13682092555331993</v>
+        <v>0.12352941176470589</v>
       </c>
       <c r="O10" s="5">
-        <v>0.13509060955518945</v>
+        <v>0.13548387096774195</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,46 +1028,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F11" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H11" s="4">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I11" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K11" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L11" s="4">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="M11" s="4">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N11" s="4">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="O11" s="4">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1075,46 +1075,46 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4">
         <v>2</v>
       </c>
-      <c r="C12" s="4">
+      <c r="D12" s="4">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4">
         <v>3</v>
       </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
       <c r="F12" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H12" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4">
+        <v>12</v>
+      </c>
+      <c r="K12" s="4">
+        <v>8</v>
+      </c>
+      <c r="L12" s="4">
+        <v>8</v>
+      </c>
+      <c r="M12" s="4">
+        <v>8</v>
+      </c>
+      <c r="N12" s="4">
+        <v>11</v>
+      </c>
+      <c r="O12" s="4">
         <v>7</v>
-      </c>
-      <c r="K12" s="4">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4">
-        <v>3</v>
-      </c>
-      <c r="M12" s="4">
-        <v>4</v>
-      </c>
-      <c r="N12" s="4">
-        <v>5</v>
-      </c>
-      <c r="O12" s="4">
-        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1122,46 +1122,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="C13" s="5">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.30434782608695654</v>
       </c>
       <c r="E13" s="5">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F13" s="5">
-        <v>0.42857142857142855</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="5">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="H13" s="5">
-        <v>0.36363636363636365</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="5">
-        <v>0.5</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="J13" s="5">
-        <v>0.7777777777777778</v>
+        <v>0.48</v>
       </c>
       <c r="K13" s="5">
         <v>0.3333333333333333</v>
       </c>
       <c r="L13" s="5">
-        <v>0.5</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="M13" s="5">
-        <v>0.4444444444444444</v>
+        <v>0.27586206896551724</v>
       </c>
       <c r="N13" s="5">
-        <v>0.4166666666666667</v>
+        <v>0.21153846153846154</v>
       </c>
       <c r="O13" s="5">
-        <v>0.2222222222222222</v>
+        <v>0.21875</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1169,43 +1169,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
       </c>
       <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>3</v>
+      </c>
+      <c r="M14" s="4">
         <v>1</v>
       </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
       <c r="N14" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" s="4">
         <v>0</v>
@@ -1246,13 +1246,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="4">
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="4">
         <v>0</v>
@@ -1262,27 +1262,29 @@
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5">
-        <v>0</v>
-      </c>
+      <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
+      <c r="L16" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="O16" s="5"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-09-28 至 2026-10-11</t>
+    <t>2026-10-05 至 2026-10-18</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C1" s="2">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="D1" s="2">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="E1" s="2">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="F1" s="2">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="G1" s="2">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="H1" s="2">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="I1" s="2">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="J1" s="2">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="K1" s="2">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="L1" s="2">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="M1" s="2">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="N1" s="2">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="O1" s="2">
-        <v>46306</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>11134</v>
+        <v>13995</v>
       </c>
       <c r="C2" s="4">
-        <v>11757</v>
+        <v>16639</v>
       </c>
       <c r="D2" s="4">
-        <v>14039</v>
+        <v>14719</v>
       </c>
       <c r="E2" s="4">
-        <v>10810</v>
+        <v>14243</v>
       </c>
       <c r="F2" s="4">
-        <v>11219</v>
+        <v>17675</v>
       </c>
       <c r="G2" s="4">
-        <v>13855</v>
+        <v>17329</v>
       </c>
       <c r="H2" s="4">
-        <v>21135</v>
+        <v>19390</v>
       </c>
       <c r="I2" s="4">
-        <v>13995</v>
+        <v>18305</v>
       </c>
       <c r="J2" s="4">
-        <v>16639</v>
+        <v>12663</v>
       </c>
       <c r="K2" s="4">
-        <v>14719</v>
+        <v>12231</v>
       </c>
       <c r="L2" s="4">
-        <v>14243</v>
+        <v>7251</v>
       </c>
       <c r="M2" s="4">
-        <v>17675</v>
+        <v>12642</v>
       </c>
       <c r="N2" s="4">
-        <v>17329</v>
+        <v>11595</v>
       </c>
       <c r="O2" s="4">
-        <v>19390</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1462</v>
+        <v>1341</v>
       </c>
       <c r="C3" s="4">
-        <v>1530</v>
+        <v>1710</v>
       </c>
       <c r="D3" s="4">
-        <v>1369</v>
+        <v>1568</v>
       </c>
       <c r="E3" s="4">
-        <v>1070</v>
+        <v>1325</v>
       </c>
       <c r="F3" s="4">
-        <v>1131</v>
+        <v>1634</v>
       </c>
       <c r="G3" s="4">
-        <v>1466</v>
+        <v>2052</v>
       </c>
       <c r="H3" s="4">
-        <v>2073</v>
+        <v>2669</v>
       </c>
       <c r="I3" s="4">
-        <v>1341</v>
+        <v>2382</v>
       </c>
       <c r="J3" s="4">
-        <v>1710</v>
+        <v>1867</v>
       </c>
       <c r="K3" s="4">
-        <v>1568</v>
+        <v>1714</v>
       </c>
       <c r="L3" s="4">
-        <v>1325</v>
+        <v>964</v>
       </c>
       <c r="M3" s="4">
-        <v>1634</v>
+        <v>1764</v>
       </c>
       <c r="N3" s="4">
-        <v>2052</v>
+        <v>1639</v>
       </c>
       <c r="O3" s="4">
-        <v>2669</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.1313095024250045</v>
+        <v>0.09581993569131833</v>
       </c>
       <c r="C4" s="5">
-        <v>0.13013523858127074</v>
+        <v>0.10277059919466314</v>
       </c>
       <c r="D4" s="5">
-        <v>0.09751406795355795</v>
+        <v>0.10652897615327128</v>
       </c>
       <c r="E4" s="5">
-        <v>0.09898242368177614</v>
+        <v>0.09302815418100119</v>
       </c>
       <c r="F4" s="5">
-        <v>0.10081112398609501</v>
+        <v>0.09244695898161245</v>
       </c>
       <c r="G4" s="5">
-        <v>0.10581017683146879</v>
+        <v>0.11841421893935022</v>
       </c>
       <c r="H4" s="5">
-        <v>0.09808374733853797</v>
+        <v>0.137648272305312</v>
       </c>
       <c r="I4" s="5">
-        <v>0.09581993569131833</v>
+        <v>0.13012838022398251</v>
       </c>
       <c r="J4" s="5">
-        <v>0.10277059919466314</v>
+        <v>0.14743741609413252</v>
       </c>
       <c r="K4" s="5">
-        <v>0.10652897615327128</v>
+        <v>0.14013572070967215</v>
       </c>
       <c r="L4" s="5">
-        <v>0.09302815418100119</v>
+        <v>0.13294717969935183</v>
       </c>
       <c r="M4" s="5">
-        <v>0.09244695898161245</v>
+        <v>0.13953488372093023</v>
       </c>
       <c r="N4" s="5">
-        <v>0.11841421893935022</v>
+        <v>0.14135403191030615</v>
       </c>
       <c r="O4" s="5">
-        <v>0.137648272305312</v>
+        <v>0.5672599941639919</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.4452804377564978</v>
+        <v>1.4556301267710663</v>
       </c>
       <c r="C5" s="6">
-        <v>1.5143790849673202</v>
+        <v>1.4210526315789473</v>
       </c>
       <c r="D5" s="6">
-        <v>1.5135135135135136</v>
+        <v>1.4732142857142858</v>
       </c>
       <c r="E5" s="6">
-        <v>1.3831775700934579</v>
+        <v>1.5192452830188679</v>
       </c>
       <c r="F5" s="6">
-        <v>1.4367816091954022</v>
+        <v>1.5379436964504285</v>
       </c>
       <c r="G5" s="6">
-        <v>1.4311050477489768</v>
+        <v>1.5243664717348928</v>
       </c>
       <c r="H5" s="6">
-        <v>1.442836468885673</v>
+        <v>1.5395279130760584</v>
       </c>
       <c r="I5" s="6">
-        <v>1.4556301267710663</v>
+        <v>1.4899244332493702</v>
       </c>
       <c r="J5" s="6">
-        <v>1.4210526315789473</v>
+        <v>1.552222817354044</v>
       </c>
       <c r="K5" s="6">
-        <v>1.4732142857142858</v>
+        <v>1.4778296382730456</v>
       </c>
       <c r="L5" s="6">
-        <v>1.5192452830188679</v>
+        <v>1.5103734439834025</v>
       </c>
       <c r="M5" s="6">
-        <v>1.5379436964504285</v>
+        <v>1.5164399092970522</v>
       </c>
       <c r="N5" s="6">
-        <v>1.5243664717348928</v>
+        <v>1.533862111043319</v>
       </c>
       <c r="O5" s="6">
-        <v>1.5395279130760584</v>
+        <v>1.5447530864197532</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="C6" s="4">
         <v>369</v>
       </c>
       <c r="D6" s="4">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="E6" s="4">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="F6" s="4">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="G6" s="4">
-        <v>303</v>
+        <v>485</v>
       </c>
       <c r="H6" s="4">
-        <v>453</v>
+        <v>646</v>
       </c>
       <c r="I6" s="4">
-        <v>301</v>
+        <v>515</v>
       </c>
       <c r="J6" s="4">
-        <v>369</v>
+        <v>470</v>
       </c>
       <c r="K6" s="4">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="L6" s="4">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="M6" s="4">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="N6" s="4">
-        <v>485</v>
+        <v>397</v>
       </c>
       <c r="O6" s="4">
-        <v>646</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.2359781121751026</v>
+        <v>0.2244593586875466</v>
       </c>
       <c r="C7" s="5">
-        <v>0.2411764705882353</v>
+        <v>0.21578947368421053</v>
       </c>
       <c r="D7" s="5">
-        <v>0.24470416362308253</v>
+        <v>0.22385204081632654</v>
       </c>
       <c r="E7" s="5">
-        <v>0.20186915887850468</v>
+        <v>0.22943396226415094</v>
       </c>
       <c r="F7" s="5">
-        <v>0.21220159151193635</v>
+        <v>0.23684210526315788</v>
       </c>
       <c r="G7" s="5">
-        <v>0.20668485675306958</v>
+        <v>0.23635477582846004</v>
       </c>
       <c r="H7" s="5">
-        <v>0.21852387843704776</v>
+        <v>0.24203821656050956</v>
       </c>
       <c r="I7" s="5">
-        <v>0.2244593586875466</v>
+        <v>0.2162048698572628</v>
       </c>
       <c r="J7" s="5">
-        <v>0.21578947368421053</v>
+        <v>0.2517407605784681</v>
       </c>
       <c r="K7" s="5">
-        <v>0.22385204081632654</v>
+        <v>0.2234539089848308</v>
       </c>
       <c r="L7" s="5">
-        <v>0.22943396226415094</v>
+        <v>0.245850622406639</v>
       </c>
       <c r="M7" s="5">
-        <v>0.23684210526315788</v>
+        <v>0.23979591836734693</v>
       </c>
       <c r="N7" s="5">
-        <v>0.23635477582846004</v>
+        <v>0.2422208663819402</v>
       </c>
       <c r="O7" s="5">
-        <v>0.24203821656050956</v>
+        <v>0.23919753086419754</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>268</v>
+        <v>450</v>
       </c>
       <c r="C8" s="4">
-        <v>251</v>
+        <v>507</v>
       </c>
       <c r="D8" s="4">
-        <v>406</v>
+        <v>455</v>
       </c>
       <c r="E8" s="4">
-        <v>303</v>
+        <v>392</v>
       </c>
       <c r="F8" s="4">
-        <v>304</v>
+        <v>519</v>
       </c>
       <c r="G8" s="4">
-        <v>405</v>
+        <v>680</v>
       </c>
       <c r="H8" s="4">
-        <v>608</v>
+        <v>930</v>
       </c>
       <c r="I8" s="4">
-        <v>450</v>
+        <v>272</v>
       </c>
       <c r="J8" s="4">
-        <v>507</v>
+        <v>164</v>
       </c>
       <c r="K8" s="4">
-        <v>455</v>
+        <v>122</v>
       </c>
       <c r="L8" s="4">
-        <v>392</v>
+        <v>75</v>
       </c>
       <c r="M8" s="4">
-        <v>519</v>
+        <v>107</v>
       </c>
       <c r="N8" s="4">
-        <v>680</v>
+        <v>188</v>
       </c>
       <c r="O8" s="4">
-        <v>930</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D9" s="4">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F9" s="4">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G9" s="4">
+        <v>84</v>
+      </c>
+      <c r="H9" s="4">
+        <v>126</v>
+      </c>
+      <c r="I9" s="4">
+        <v>74</v>
+      </c>
+      <c r="J9" s="4">
+        <v>48</v>
+      </c>
+      <c r="K9" s="4">
+        <v>20</v>
+      </c>
+      <c r="L9" s="4">
+        <v>24</v>
+      </c>
+      <c r="M9" s="4">
+        <v>35</v>
+      </c>
+      <c r="N9" s="4">
         <v>40</v>
       </c>
-      <c r="H9" s="4">
-        <v>88</v>
-      </c>
-      <c r="I9" s="4">
-        <v>59</v>
-      </c>
-      <c r="J9" s="4">
-        <v>95</v>
-      </c>
-      <c r="K9" s="4">
-        <v>50</v>
-      </c>
-      <c r="L9" s="4">
-        <v>69</v>
-      </c>
-      <c r="M9" s="4">
-        <v>85</v>
-      </c>
-      <c r="N9" s="4">
-        <v>84</v>
-      </c>
       <c r="O9" s="4">
-        <v>126</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.3283582089552239</v>
+        <v>0.13111111111111112</v>
       </c>
       <c r="C10" s="5">
-        <v>0.32270916334661354</v>
+        <v>0.1873767258382643</v>
       </c>
       <c r="D10" s="5">
-        <v>0.11576354679802955</v>
+        <v>0.10989010989010989</v>
       </c>
       <c r="E10" s="5">
-        <v>0.0891089108910891</v>
+        <v>0.1760204081632653</v>
       </c>
       <c r="F10" s="5">
-        <v>0.09539473684210527</v>
+        <v>0.16377649325626203</v>
       </c>
       <c r="G10" s="5">
-        <v>0.09876543209876543</v>
+        <v>0.12352941176470589</v>
       </c>
       <c r="H10" s="5">
-        <v>0.14473684210526316</v>
+        <v>0.13548387096774195</v>
       </c>
       <c r="I10" s="5">
-        <v>0.13111111111111112</v>
+        <v>0.27205882352941174</v>
       </c>
       <c r="J10" s="5">
-        <v>0.1873767258382643</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="K10" s="5">
-        <v>0.10989010989010989</v>
+        <v>0.16393442622950818</v>
       </c>
       <c r="L10" s="5">
-        <v>0.1760204081632653</v>
+        <v>0.32</v>
       </c>
       <c r="M10" s="5">
-        <v>0.16377649325626203</v>
+        <v>0.32710280373831774</v>
       </c>
       <c r="N10" s="5">
-        <v>0.12352941176470589</v>
+        <v>0.2127659574468085</v>
       </c>
       <c r="O10" s="5">
-        <v>0.13548387096774195</v>
+        <v>0.17857142857142858</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,163 +1028,157 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" s="4">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G11" s="4">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H11" s="4">
         <v>32</v>
       </c>
       <c r="I11" s="4">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J11" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K11" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M11" s="4">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="N11" s="4">
-        <v>52</v>
-      </c>
-      <c r="O11" s="4">
-        <v>32</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4">
+        <v>8</v>
+      </c>
+      <c r="G12" s="4">
+        <v>11</v>
+      </c>
+      <c r="H12" s="4">
+        <v>7</v>
+      </c>
+      <c r="I12" s="4">
+        <v>11</v>
+      </c>
+      <c r="J12" s="4">
         <v>5</v>
       </c>
-      <c r="C12" s="4">
-        <v>2</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="K12" s="4">
+        <v>10</v>
+      </c>
+      <c r="L12" s="4">
         <v>7</v>
       </c>
-      <c r="E12" s="4">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4">
-        <v>4</v>
-      </c>
-      <c r="G12" s="4">
-        <v>7</v>
-      </c>
-      <c r="H12" s="4">
-        <v>8</v>
-      </c>
-      <c r="I12" s="4">
-        <v>8</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="M12" s="4">
         <v>12</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
-        <v>8</v>
-      </c>
-      <c r="M12" s="4">
-        <v>8</v>
-      </c>
       <c r="N12" s="4">
-        <v>11</v>
-      </c>
-      <c r="O12" s="4">
-        <v>7</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="O12" s="4"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.38461538461538464</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="C13" s="5">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="D13" s="5">
-        <v>0.30434782608695654</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E13" s="5">
-        <v>0.25</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F13" s="5">
-        <v>0.4</v>
+        <v>0.27586206896551724</v>
       </c>
       <c r="G13" s="5">
-        <v>0.4375</v>
+        <v>0.21153846153846154</v>
       </c>
       <c r="H13" s="5">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="I13" s="5">
-        <v>0.42105263157894735</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="J13" s="5">
-        <v>0.48</v>
+        <v>0.21739130434782608</v>
       </c>
       <c r="K13" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="L13" s="5">
-        <v>0.2962962962962963</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="M13" s="5">
-        <v>0.27586206896551724</v>
+        <v>0.27906976744186046</v>
       </c>
       <c r="N13" s="5">
-        <v>0.21153846153846154</v>
-      </c>
-      <c r="O13" s="5">
-        <v>0.21875</v>
-      </c>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4">
         <v>0</v>
@@ -1193,23 +1187,21 @@
         <v>0</v>
       </c>
       <c r="J14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>3</v>
-      </c>
-      <c r="O14" s="4">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O14" s="4"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -1225,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
@@ -1246,45 +1238,41 @@
         <v>0</v>
       </c>
       <c r="L15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="4">
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>1</v>
-      </c>
-      <c r="O15" s="4">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O15" s="4"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="E16" s="5">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5">
-        <v>0.3333333333333333</v>
-      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
       <c r="O16" s="5"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1330,9 +1318,7 @@
       <c r="N17" s="4">
         <v>0</v>
       </c>
-      <c r="O17" s="4">
-        <v>0</v>
-      </c>
+      <c r="O17" s="4"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -1377,9 +1363,7 @@
       <c r="N18" s="4">
         <v>0</v>
       </c>
-      <c r="O18" s="4">
-        <v>0</v>
-      </c>
+      <c r="O18" s="4"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="C8" s="4">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="D8" s="4">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E8" s="4">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F8" s="4">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="G8" s="4">
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="H8" s="4">
-        <v>930</v>
+        <v>951</v>
       </c>
       <c r="I8" s="4">
-        <v>272</v>
+        <v>652</v>
       </c>
       <c r="J8" s="4">
-        <v>164</v>
+        <v>490</v>
       </c>
       <c r="K8" s="4">
-        <v>122</v>
+        <v>480</v>
       </c>
       <c r="L8" s="4">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="M8" s="4">
-        <v>107</v>
+        <v>541</v>
       </c>
       <c r="N8" s="4">
-        <v>188</v>
+        <v>521</v>
       </c>
       <c r="O8" s="4">
-        <v>84</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C9" s="4">
         <v>95</v>
       </c>
       <c r="D9" s="4">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E9" s="4">
         <v>69</v>
       </c>
       <c r="F9" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="4">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H9" s="4">
         <v>126</v>
       </c>
       <c r="I9" s="4">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="J9" s="4">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="K9" s="4">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L9" s="4">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="M9" s="4">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="N9" s="4">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O9" s="4">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.13111111111111112</v>
+        <v>0.17204301075268819</v>
       </c>
       <c r="C10" s="5">
-        <v>0.1873767258382643</v>
+        <v>0.18410852713178294</v>
       </c>
       <c r="D10" s="5">
-        <v>0.10989010989010989</v>
+        <v>0.16052060737527116</v>
       </c>
       <c r="E10" s="5">
-        <v>0.1760204081632653</v>
+        <v>0.17336683417085427</v>
       </c>
       <c r="F10" s="5">
-        <v>0.16377649325626203</v>
+        <v>0.16104868913857678</v>
       </c>
       <c r="G10" s="5">
-        <v>0.12352941176470589</v>
+        <v>0.16305916305916307</v>
       </c>
       <c r="H10" s="5">
-        <v>0.13548387096774195</v>
+        <v>0.13249211356466878</v>
       </c>
       <c r="I10" s="5">
-        <v>0.27205882352941174</v>
+        <v>0.16104294478527606</v>
       </c>
       <c r="J10" s="5">
-        <v>0.2926829268292683</v>
+        <v>0.1653061224489796</v>
       </c>
       <c r="K10" s="5">
-        <v>0.16393442622950818</v>
+        <v>0.10625</v>
       </c>
       <c r="L10" s="5">
-        <v>0.32</v>
+        <v>0.18726591760299627</v>
       </c>
       <c r="M10" s="5">
-        <v>0.32710280373831774</v>
+        <v>0.12384473197781885</v>
       </c>
       <c r="N10" s="5">
-        <v>0.2127659574468085</v>
+        <v>0.13051823416506717</v>
       </c>
       <c r="O10" s="5">
-        <v>0.17857142857142858</v>
+        <v>0.13218390804597702</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -644,7 +644,7 @@
         <v>11595</v>
       </c>
       <c r="O2" s="4">
-        <v>3427</v>
+        <v>15020</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -738,7 +738,7 @@
         <v>0.14135403191030615</v>
       </c>
       <c r="O4" s="5">
-        <v>0.5672599941639919</v>
+        <v>0.12942743009320906</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -926,7 +926,7 @@
         <v>521</v>
       </c>
       <c r="O8" s="4">
-        <v>174</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>68</v>
       </c>
       <c r="O9" s="4">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1020,7 +1020,7 @@
         <v>0.13051823416506717</v>
       </c>
       <c r="O10" s="5">
-        <v>0.13218390804597702</v>
+        <v>0.1580547112462006</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1066,7 +1066,9 @@
       <c r="N11" s="4">
         <v>35</v>
       </c>
-      <c r="O11" s="4"/>
+      <c r="O11" s="4">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -1111,7 +1113,9 @@
       <c r="N12" s="4">
         <v>10</v>
       </c>
-      <c r="O12" s="4"/>
+      <c r="O12" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1156,7 +1160,9 @@
       <c r="N13" s="5">
         <v>0.2857142857142857</v>
       </c>
-      <c r="O13" s="5"/>
+      <c r="O13" s="5">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -1201,7 +1207,9 @@
       <c r="N14" s="4">
         <v>0</v>
       </c>
-      <c r="O14" s="4"/>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -1246,7 +1254,9 @@
       <c r="N15" s="4">
         <v>0</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -1318,7 +1328,9 @@
       <c r="N17" s="4">
         <v>0</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -1363,7 +1375,9 @@
       <c r="N18" s="4">
         <v>0</v>
       </c>
-      <c r="O18" s="4"/>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -926,7 +926,7 @@
         <v>521</v>
       </c>
       <c r="O8" s="4">
-        <v>329</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>68</v>
       </c>
       <c r="O9" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1020,7 +1020,7 @@
         <v>0.13051823416506717</v>
       </c>
       <c r="O10" s="5">
-        <v>0.1580547112462006</v>
+        <v>0.1252336448598131</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-10-05 至 2026-10-18</t>
+    <t>2026-10-12 至 2026-10-25</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C1" s="2">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="D1" s="2">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="E1" s="2">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="F1" s="2">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="G1" s="2">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="H1" s="2">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="I1" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="J1" s="2">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="K1" s="2">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="L1" s="2">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="M1" s="2">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="N1" s="2">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="O1" s="2">
-        <v>46313</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>13995</v>
+        <v>18305</v>
       </c>
       <c r="C2" s="4">
-        <v>16639</v>
+        <v>12663</v>
       </c>
       <c r="D2" s="4">
-        <v>14719</v>
+        <v>12231</v>
       </c>
       <c r="E2" s="4">
-        <v>14243</v>
+        <v>7251</v>
       </c>
       <c r="F2" s="4">
-        <v>17675</v>
+        <v>12642</v>
       </c>
       <c r="G2" s="4">
-        <v>17329</v>
+        <v>11595</v>
       </c>
       <c r="H2" s="4">
-        <v>19390</v>
+        <v>15020</v>
       </c>
       <c r="I2" s="4">
-        <v>18305</v>
+        <v>12242</v>
       </c>
       <c r="J2" s="4">
-        <v>12663</v>
+        <v>8668</v>
       </c>
       <c r="K2" s="4">
-        <v>12231</v>
+        <v>2278</v>
       </c>
       <c r="L2" s="4">
-        <v>7251</v>
+        <v>1486</v>
       </c>
       <c r="M2" s="4">
-        <v>12642</v>
+        <v>2387</v>
       </c>
       <c r="N2" s="4">
-        <v>11595</v>
+        <v>4709</v>
       </c>
       <c r="O2" s="4">
-        <v>15020</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1341</v>
+        <v>2382</v>
       </c>
       <c r="C3" s="4">
-        <v>1710</v>
+        <v>1867</v>
       </c>
       <c r="D3" s="4">
-        <v>1568</v>
+        <v>1714</v>
       </c>
       <c r="E3" s="4">
-        <v>1325</v>
+        <v>964</v>
       </c>
       <c r="F3" s="4">
-        <v>1634</v>
+        <v>1764</v>
       </c>
       <c r="G3" s="4">
-        <v>2052</v>
+        <v>1639</v>
       </c>
       <c r="H3" s="4">
-        <v>2669</v>
+        <v>1944</v>
       </c>
       <c r="I3" s="4">
-        <v>2382</v>
+        <v>1347</v>
       </c>
       <c r="J3" s="4">
-        <v>1867</v>
+        <v>989</v>
       </c>
       <c r="K3" s="4">
-        <v>1714</v>
+        <v>207</v>
       </c>
       <c r="L3" s="4">
-        <v>964</v>
+        <v>142</v>
       </c>
       <c r="M3" s="4">
-        <v>1764</v>
+        <v>247</v>
       </c>
       <c r="N3" s="4">
-        <v>1639</v>
+        <v>635</v>
       </c>
       <c r="O3" s="4">
-        <v>1944</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.09581993569131833</v>
+        <v>0.13012838022398251</v>
       </c>
       <c r="C4" s="5">
-        <v>0.10277059919466314</v>
+        <v>0.14743741609413252</v>
       </c>
       <c r="D4" s="5">
-        <v>0.10652897615327128</v>
+        <v>0.14013572070967215</v>
       </c>
       <c r="E4" s="5">
-        <v>0.09302815418100119</v>
+        <v>0.13294717969935183</v>
       </c>
       <c r="F4" s="5">
-        <v>0.09244695898161245</v>
+        <v>0.13953488372093023</v>
       </c>
       <c r="G4" s="5">
-        <v>0.11841421893935022</v>
+        <v>0.14135403191030615</v>
       </c>
       <c r="H4" s="5">
-        <v>0.137648272305312</v>
+        <v>0.12942743009320906</v>
       </c>
       <c r="I4" s="5">
-        <v>0.13012838022398251</v>
+        <v>0.11003104067962752</v>
       </c>
       <c r="J4" s="5">
-        <v>0.14743741609413252</v>
+        <v>0.11409783110290725</v>
       </c>
       <c r="K4" s="5">
-        <v>0.14013572070967215</v>
+        <v>0.09086918349429324</v>
       </c>
       <c r="L4" s="5">
-        <v>0.13294717969935183</v>
+        <v>0.0955585464333782</v>
       </c>
       <c r="M4" s="5">
-        <v>0.13953488372093023</v>
+        <v>0.10347716799329702</v>
       </c>
       <c r="N4" s="5">
-        <v>0.14135403191030615</v>
+        <v>0.13484816309195158</v>
       </c>
       <c r="O4" s="5">
-        <v>0.12942743009320906</v>
+        <v>0.14520676691729323</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.4556301267710663</v>
+        <v>1.4899244332493702</v>
       </c>
       <c r="C5" s="6">
-        <v>1.4210526315789473</v>
+        <v>1.552222817354044</v>
       </c>
       <c r="D5" s="6">
-        <v>1.4732142857142858</v>
+        <v>1.4778296382730456</v>
       </c>
       <c r="E5" s="6">
-        <v>1.5192452830188679</v>
+        <v>1.5103734439834025</v>
       </c>
       <c r="F5" s="6">
-        <v>1.5379436964504285</v>
+        <v>1.5164399092970522</v>
       </c>
       <c r="G5" s="6">
-        <v>1.5243664717348928</v>
+        <v>1.533862111043319</v>
       </c>
       <c r="H5" s="6">
-        <v>1.5395279130760584</v>
+        <v>1.5447530864197532</v>
       </c>
       <c r="I5" s="6">
-        <v>1.4899244332493702</v>
+        <v>1.5189309576837418</v>
       </c>
       <c r="J5" s="6">
-        <v>1.552222817354044</v>
+        <v>1.6481294236602628</v>
       </c>
       <c r="K5" s="6">
-        <v>1.4778296382730456</v>
+        <v>1.603864734299517</v>
       </c>
       <c r="L5" s="6">
-        <v>1.5103734439834025</v>
+        <v>1.5633802816901408</v>
       </c>
       <c r="M5" s="6">
-        <v>1.5164399092970522</v>
+        <v>1.4129554655870444</v>
       </c>
       <c r="N5" s="6">
-        <v>1.533862111043319</v>
+        <v>1.462992125984252</v>
       </c>
       <c r="O5" s="6">
-        <v>1.5447530864197532</v>
+        <v>1.6067961165048543</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>301</v>
+        <v>515</v>
       </c>
       <c r="C6" s="4">
-        <v>369</v>
+        <v>470</v>
       </c>
       <c r="D6" s="4">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="E6" s="4">
-        <v>304</v>
+        <v>237</v>
       </c>
       <c r="F6" s="4">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="G6" s="4">
-        <v>485</v>
+        <v>397</v>
       </c>
       <c r="H6" s="4">
-        <v>646</v>
+        <v>465</v>
       </c>
       <c r="I6" s="4">
-        <v>515</v>
+        <v>313</v>
       </c>
       <c r="J6" s="4">
-        <v>470</v>
+        <v>280</v>
       </c>
       <c r="K6" s="4">
-        <v>383</v>
+        <v>58</v>
       </c>
       <c r="L6" s="4">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="M6" s="4">
-        <v>423</v>
+        <v>58</v>
       </c>
       <c r="N6" s="4">
-        <v>397</v>
+        <v>152</v>
       </c>
       <c r="O6" s="4">
-        <v>465</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.2244593586875466</v>
+        <v>0.2162048698572628</v>
       </c>
       <c r="C7" s="5">
-        <v>0.21578947368421053</v>
+        <v>0.2517407605784681</v>
       </c>
       <c r="D7" s="5">
-        <v>0.22385204081632654</v>
+        <v>0.2234539089848308</v>
       </c>
       <c r="E7" s="5">
-        <v>0.22943396226415094</v>
+        <v>0.245850622406639</v>
       </c>
       <c r="F7" s="5">
-        <v>0.23684210526315788</v>
+        <v>0.23979591836734693</v>
       </c>
       <c r="G7" s="5">
-        <v>0.23635477582846004</v>
+        <v>0.2422208663819402</v>
       </c>
       <c r="H7" s="5">
-        <v>0.24203821656050956</v>
+        <v>0.23919753086419754</v>
       </c>
       <c r="I7" s="5">
-        <v>0.2162048698572628</v>
+        <v>0.2323682256867112</v>
       </c>
       <c r="J7" s="5">
-        <v>0.2517407605784681</v>
+        <v>0.28311425682507585</v>
       </c>
       <c r="K7" s="5">
-        <v>0.2234539089848308</v>
+        <v>0.28019323671497587</v>
       </c>
       <c r="L7" s="5">
-        <v>0.245850622406639</v>
+        <v>0.21830985915492956</v>
       </c>
       <c r="M7" s="5">
-        <v>0.23979591836734693</v>
+        <v>0.23481781376518218</v>
       </c>
       <c r="N7" s="5">
-        <v>0.2422208663819402</v>
+        <v>0.23937007874015748</v>
       </c>
       <c r="O7" s="5">
-        <v>0.23919753086419754</v>
+        <v>0.27993527508090615</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>465</v>
+        <v>652</v>
       </c>
       <c r="C8" s="4">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="D8" s="4">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="E8" s="4">
-        <v>398</v>
+        <v>267</v>
       </c>
       <c r="F8" s="4">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G8" s="4">
-        <v>693</v>
+        <v>521</v>
       </c>
       <c r="H8" s="4">
-        <v>951</v>
+        <v>535</v>
       </c>
       <c r="I8" s="4">
-        <v>652</v>
+        <v>377</v>
       </c>
       <c r="J8" s="4">
-        <v>490</v>
+        <v>210</v>
       </c>
       <c r="K8" s="4">
-        <v>480</v>
+        <v>52</v>
       </c>
       <c r="L8" s="4">
-        <v>267</v>
+        <v>29</v>
       </c>
       <c r="M8" s="4">
-        <v>541</v>
+        <v>56</v>
       </c>
       <c r="N8" s="4">
-        <v>521</v>
+        <v>143</v>
       </c>
       <c r="O8" s="4">
-        <v>535</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C9" s="4">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D9" s="4">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="E9" s="4">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="G9" s="4">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H9" s="4">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="I9" s="4">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="J9" s="4">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="K9" s="4">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="L9" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M9" s="4">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="O9" s="4">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.17204301075268819</v>
+        <v>0.16104294478527606</v>
       </c>
       <c r="C10" s="5">
-        <v>0.18410852713178294</v>
+        <v>0.1653061224489796</v>
       </c>
       <c r="D10" s="5">
-        <v>0.16052060737527116</v>
+        <v>0.10625</v>
       </c>
       <c r="E10" s="5">
-        <v>0.17336683417085427</v>
+        <v>0.18726591760299627</v>
       </c>
       <c r="F10" s="5">
-        <v>0.16104868913857678</v>
+        <v>0.12384473197781885</v>
       </c>
       <c r="G10" s="5">
-        <v>0.16305916305916307</v>
+        <v>0.13051823416506717</v>
       </c>
       <c r="H10" s="5">
-        <v>0.13249211356466878</v>
+        <v>0.1252336448598131</v>
       </c>
       <c r="I10" s="5">
-        <v>0.16104294478527606</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="J10" s="5">
-        <v>0.1653061224489796</v>
+        <v>0.20952380952380953</v>
       </c>
       <c r="K10" s="5">
-        <v>0.10625</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="L10" s="5">
-        <v>0.18726591760299627</v>
+        <v>0.10344827586206896</v>
       </c>
       <c r="M10" s="5">
-        <v>0.12384473197781885</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="N10" s="5">
-        <v>0.13051823416506717</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="O10" s="5">
-        <v>0.1252336448598131</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,46 +1028,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G11" s="4">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H11" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J11" s="4">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K11" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L11" s="4">
+        <v>14</v>
+      </c>
+      <c r="M11" s="4">
         <v>18</v>
       </c>
-      <c r="M11" s="4">
-        <v>43</v>
-      </c>
       <c r="N11" s="4">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="O11" s="4">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1075,46 +1075,46 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4">
         <v>12</v>
       </c>
-      <c r="D12" s="4">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4">
-        <v>8</v>
-      </c>
       <c r="G12" s="4">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4">
         <v>11</v>
       </c>
-      <c r="H12" s="4">
-        <v>7</v>
-      </c>
       <c r="I12" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4">
+        <v>12</v>
+      </c>
+      <c r="K12" s="4">
         <v>5</v>
       </c>
-      <c r="K12" s="4">
-        <v>10</v>
-      </c>
       <c r="L12" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M12" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O12" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1122,46 +1122,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.42105263157894735</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="C13" s="5">
-        <v>0.48</v>
+        <v>0.21739130434782608</v>
       </c>
       <c r="D13" s="5">
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H13" s="5">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E13" s="5">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.27586206896551724</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.21153846153846154</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.21875</v>
-      </c>
       <c r="I13" s="5">
-        <v>0.2894736842105263</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="J13" s="5">
-        <v>0.21739130434782608</v>
+        <v>0.24489795918367346</v>
       </c>
       <c r="K13" s="5">
-        <v>0.43478260869565216</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="L13" s="5">
-        <v>0.3888888888888889</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="M13" s="5">
-        <v>0.27906976744186046</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>0.2857142857142857</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="O13" s="5">
-        <v>0.3333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1172,25 +1172,25 @@
         <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
       </c>
       <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
         <v>3</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4">
-        <v>3</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0</v>
       </c>
       <c r="J14" s="4">
         <v>1</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="4">
         <v>0</v>
@@ -1225,28 +1225,28 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>3</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
         <v>1</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0</v>
       </c>
       <c r="M15" s="4">
         <v>0</v>
@@ -1263,24 +1263,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5">
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
